--- a/outputs/cumulative_motion_statistics.xlsx
+++ b/outputs/cumulative_motion_statistics.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="cumulative_rotation_by_arm" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="summary_table_for_cumulative_rotation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cumulative_rotation_summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,10 +441,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15149.60308938232</v>
+        <v>15149.60308937928</v>
       </c>
       <c r="C2" t="n">
-        <v>17467.51276178188</v>
+        <v>17467.51276177059</v>
       </c>
     </row>
     <row r="3">
@@ -454,10 +454,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19398.08254799702</v>
+        <v>19398.08254855897</v>
       </c>
       <c r="C3" t="n">
-        <v>19499.19261242916</v>
+        <v>19499.19261239495</v>
       </c>
     </row>
     <row r="4">
@@ -467,10 +467,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7370.600731923303</v>
+        <v>7370.60073219791</v>
       </c>
       <c r="C4" t="n">
-        <v>9154.809543741259</v>
+        <v>9154.809543875186</v>
       </c>
     </row>
     <row r="5">
@@ -480,10 +480,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7755.942344052965</v>
+        <v>7755.942344182265</v>
       </c>
       <c r="C5" t="n">
-        <v>6007.159162029807</v>
+        <v>6007.159162004044</v>
       </c>
     </row>
     <row r="6">
@@ -493,10 +493,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26538.15689684161</v>
+        <v>26538.15689682981</v>
       </c>
       <c r="C6" t="n">
-        <v>27373.58243923739</v>
+        <v>27373.58243922007</v>
       </c>
     </row>
     <row r="7">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9309.827607044062</v>
+        <v>9309.827607046343</v>
       </c>
       <c r="C7" t="n">
-        <v>7812.593924312177</v>
+        <v>7812.593924313127</v>
       </c>
     </row>
     <row r="8">
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10169.41192568947</v>
+        <v>10169.41192585171</v>
       </c>
       <c r="C8" t="n">
-        <v>16296.66339064303</v>
+        <v>16296.66339063944</v>
       </c>
     </row>
     <row r="9">
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13911.20193562416</v>
+        <v>13911.20193559942</v>
       </c>
       <c r="C9" t="n">
-        <v>13072.54596714714</v>
+        <v>13072.54596750392</v>
       </c>
     </row>
     <row r="10">
@@ -545,10 +545,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10518.75454174527</v>
+        <v>10518.75454174541</v>
       </c>
       <c r="C10" t="n">
-        <v>9881.91421985705</v>
+        <v>9881.914219836446</v>
       </c>
     </row>
     <row r="11">
@@ -558,10 +558,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20046.33529758643</v>
+        <v>20046.33529756156</v>
       </c>
       <c r="C11" t="n">
-        <v>19394.28672103599</v>
+        <v>19394.28672129683</v>
       </c>
     </row>
     <row r="12">
@@ -571,10 +571,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12041.60781965639</v>
+        <v>12041.60781965383</v>
       </c>
       <c r="C12" t="n">
-        <v>12757.86818740884</v>
+        <v>12757.8681873847</v>
       </c>
     </row>
     <row r="13">
@@ -584,10 +584,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7219.582203583178</v>
+        <v>7219.582203575899</v>
       </c>
       <c r="C13" t="n">
-        <v>10690.12483507</v>
+        <v>10690.12483506765</v>
       </c>
     </row>
     <row r="14">
@@ -597,10 +597,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11332.17206143804</v>
+        <v>11332.17206140876</v>
       </c>
       <c r="C14" t="n">
-        <v>13051.59906537385</v>
+        <v>13051.5990658314</v>
       </c>
     </row>
     <row r="15">
@@ -610,10 +610,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10478.81173727828</v>
+        <v>10478.81173767831</v>
       </c>
       <c r="C15" t="n">
-        <v>9251.117811559368</v>
+        <v>9251.117811795946</v>
       </c>
     </row>
     <row r="16">
@@ -623,10 +623,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8365.161836631061</v>
+        <v>8365.161836602292</v>
       </c>
       <c r="C16" t="n">
-        <v>6956.647770237873</v>
+        <v>6956.647770168285</v>
       </c>
     </row>
     <row r="17">
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11582.95142653832</v>
+        <v>11582.95142675634</v>
       </c>
       <c r="C17" t="n">
-        <v>11960.42411630118</v>
+        <v>11960.42411651058</v>
       </c>
     </row>
     <row r="18">
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13019.92156372705</v>
+        <v>13019.92156370074</v>
       </c>
       <c r="C18" t="n">
-        <v>13125.08729458048</v>
+        <v>13125.08729456735</v>
       </c>
     </row>
     <row r="19">
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5284.944803286417</v>
+        <v>5284.944803284073</v>
       </c>
       <c r="C19" t="n">
-        <v>5327.477792721957</v>
+        <v>5327.477792829137</v>
       </c>
     </row>
     <row r="20">
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7353.771188515191</v>
+        <v>7353.771188682915</v>
       </c>
       <c r="C20" t="n">
-        <v>6838.198884391815</v>
+        <v>6838.198884794345</v>
       </c>
     </row>
   </sheetData>
@@ -737,16 +737,16 @@
         <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>11939.3074504495</v>
+        <v>11939.30745054188</v>
       </c>
       <c r="D2" t="n">
-        <v>5287.727607550595</v>
+        <v>5287.727607554598</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.065044201231446</v>
+        <v>-1.065044201264143</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3009347841758985</v>
+        <v>0.300934784161501</v>
       </c>
     </row>
     <row r="3">
@@ -759,16 +759,16 @@
         <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>12416.77928946633</v>
+        <v>12416.77928956863</v>
       </c>
       <c r="D3" t="n">
-        <v>5619.001325794886</v>
+        <v>5619.001325775752</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.065044201231446</v>
+        <v>-1.065044201264143</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3009347841758985</v>
+        <v>0.300934784161501</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cumulative_motion_statistics.xlsx
+++ b/outputs/cumulative_motion_statistics.xlsx
@@ -441,10 +441,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15149.60308937928</v>
+        <v>15149.60308937927</v>
       </c>
       <c r="C2" t="n">
-        <v>17467.51276177059</v>
+        <v>17467.51276177058</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         <v>19398.08254855897</v>
       </c>
       <c r="C3" t="n">
-        <v>19499.19261239495</v>
+        <v>19499.19261239494</v>
       </c>
     </row>
     <row r="4">
@@ -467,10 +467,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7370.60073219791</v>
+        <v>7370.600732218009</v>
       </c>
       <c r="C4" t="n">
-        <v>9154.809543875186</v>
+        <v>9154.809543875175</v>
       </c>
     </row>
     <row r="5">
@@ -480,10 +480,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7755.942344182265</v>
+        <v>7755.942344220794</v>
       </c>
       <c r="C5" t="n">
-        <v>6007.159162004044</v>
+        <v>6007.159162004034</v>
       </c>
     </row>
     <row r="6">
@@ -493,10 +493,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26538.15689682981</v>
+        <v>26538.1568968298</v>
       </c>
       <c r="C6" t="n">
-        <v>27373.58243922007</v>
+        <v>27373.58243922011</v>
       </c>
     </row>
     <row r="7">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9309.827607046343</v>
+        <v>9309.827607109573</v>
       </c>
       <c r="C7" t="n">
-        <v>7812.593924313127</v>
+        <v>7812.593924292049</v>
       </c>
     </row>
     <row r="8">
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10169.41192585171</v>
+        <v>10169.4119258939</v>
       </c>
       <c r="C8" t="n">
-        <v>16296.66339063944</v>
+        <v>16296.66339063943</v>
       </c>
     </row>
     <row r="9">
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13911.20193559942</v>
+        <v>13911.20193557838</v>
       </c>
       <c r="C9" t="n">
-        <v>13072.54596750392</v>
+        <v>13072.54596751061</v>
       </c>
     </row>
     <row r="10">
@@ -558,10 +558,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20046.33529756156</v>
+        <v>20046.33529756153</v>
       </c>
       <c r="C11" t="n">
-        <v>19394.28672129683</v>
+        <v>19394.28672124085</v>
       </c>
     </row>
     <row r="12">
@@ -574,7 +574,7 @@
         <v>12041.60781965383</v>
       </c>
       <c r="C12" t="n">
-        <v>12757.8681873847</v>
+        <v>12757.86818740577</v>
       </c>
     </row>
     <row r="13">
@@ -584,10 +584,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7219.582203575899</v>
+        <v>7219.582203575893</v>
       </c>
       <c r="C13" t="n">
-        <v>10690.12483506765</v>
+        <v>10690.12483508874</v>
       </c>
     </row>
     <row r="14">
@@ -597,10 +597,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11332.17206140876</v>
+        <v>11332.17206140879</v>
       </c>
       <c r="C14" t="n">
-        <v>13051.5990658314</v>
+        <v>13051.5990658227</v>
       </c>
     </row>
     <row r="15">
@@ -610,10 +610,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10478.81173767831</v>
+        <v>10478.8117376896</v>
       </c>
       <c r="C15" t="n">
-        <v>9251.117811795946</v>
+        <v>9251.11781183958</v>
       </c>
     </row>
     <row r="16">
@@ -623,10 +623,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8365.161836602292</v>
+        <v>8365.161836602245</v>
       </c>
       <c r="C16" t="n">
-        <v>6956.647770168285</v>
+        <v>6956.647770168286</v>
       </c>
     </row>
     <row r="17">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11582.95142675634</v>
+        <v>11582.95142675432</v>
       </c>
       <c r="C17" t="n">
         <v>11960.42411651058</v>
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13019.92156370074</v>
+        <v>13019.92156370073</v>
       </c>
       <c r="C18" t="n">
-        <v>13125.08729456735</v>
+        <v>13125.08729456734</v>
       </c>
     </row>
     <row r="19">
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5284.944803284073</v>
+        <v>5284.944803284069</v>
       </c>
       <c r="C19" t="n">
-        <v>5327.477792829137</v>
+        <v>5327.477792808078</v>
       </c>
     </row>
     <row r="20">
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7353.771188682915</v>
+        <v>7353.771188689632</v>
       </c>
       <c r="C20" t="n">
-        <v>6838.198884794345</v>
+        <v>6838.198884789373</v>
       </c>
     </row>
   </sheetData>
@@ -737,16 +737,16 @@
         <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>11939.30745054188</v>
+        <v>11939.30745055025</v>
       </c>
       <c r="D2" t="n">
-        <v>5287.727607554598</v>
+        <v>5287.727607548481</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.065044201264143</v>
+        <v>-1.065044201242645</v>
       </c>
       <c r="F2" t="n">
-        <v>0.300934784161501</v>
+        <v>0.300934784170967</v>
       </c>
     </row>
     <row r="3">
@@ -759,16 +759,16 @@
         <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>12416.77928956863</v>
+        <v>12416.77928956762</v>
       </c>
       <c r="D3" t="n">
-        <v>5619.001325775752</v>
+        <v>5619.00132577294</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.065044201264143</v>
+        <v>-1.065044201242645</v>
       </c>
       <c r="F3" t="n">
-        <v>0.300934784161501</v>
+        <v>0.300934784170967</v>
       </c>
     </row>
   </sheetData>
